--- a/实验参数.xlsx
+++ b/实验参数.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13603\Desktop\复现\LightGCN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13603\Desktop\LightGCN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03526FE7-1332-483B-8089-638A4D885284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B4DFDD-AE54-4678-AD3B-C304EEDEF1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9360" yWindow="1485" windowWidth="17280" windowHeight="10103" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Embedding维度</t>
   </si>
@@ -43,6 +43,26 @@
   </si>
   <si>
     <t>源码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGCN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P@10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R@10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NDCG@10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -50,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +83,14 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -83,14 +111,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -368,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:J8"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.4">
@@ -448,8 +479,52 @@
         <v>3</v>
       </c>
     </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>0.1101</v>
+      </c>
+      <c r="D12">
+        <v>8.1799999999999998E-2</v>
+      </c>
+      <c r="E12">
+        <v>0.52470000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>0.10580000000000001</v>
+      </c>
+      <c r="D13">
+        <v>0.1336</v>
+      </c>
+      <c r="E13">
+        <v>0.77669999999999995</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{34E30A24-88A9-4B4A-A7D1-3797BE84AD6A}"/>
+    <hyperlink ref="D11" r:id="rId2" xr:uid="{8FF83FF7-9C6C-455E-9EBA-041CEDCC1E1B}"/>
+    <hyperlink ref="E11" r:id="rId3" xr:uid="{8DDA63BE-58DE-4070-9094-C065D1708B3E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/实验参数.xlsx
+++ b/实验参数.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13603\Desktop\LightGCN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B4DFDD-AE54-4678-AD3B-C304EEDEF1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FBB706-E526-42C3-B2DC-B2CED47A8F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="1485" windowWidth="17280" windowHeight="10103" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18090" yWindow="1935" windowWidth="19815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,14 +83,6 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -111,17 +103,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -400,14 +390,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J13"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -421,7 +411,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F4" t="s">
         <v>3</v>
       </c>
@@ -429,7 +419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>1</v>
       </c>
@@ -443,7 +433,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F6" t="s">
         <v>3</v>
       </c>
@@ -451,7 +441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -468,7 +458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F8" t="s">
         <v>3</v>
       </c>
@@ -479,7 +469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -490,7 +480,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -504,7 +494,7 @@
         <v>0.52470000000000006</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>6</v>
       </c>
@@ -520,11 +510,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1" xr:uid="{34E30A24-88A9-4B4A-A7D1-3797BE84AD6A}"/>
-    <hyperlink ref="D11" r:id="rId2" xr:uid="{8FF83FF7-9C6C-455E-9EBA-041CEDCC1E1B}"/>
-    <hyperlink ref="E11" r:id="rId3" xr:uid="{8DDA63BE-58DE-4070-9094-C065D1708B3E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>